--- a/private_equity_structured.xlsx
+++ b/private_equity_structured.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://sg.jobstreet.com/jobs-in-real-estate-property/valuation/full-time</t>
+          <t>https://jobs.temasek.com.sg/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://warburgpincus.com/careers/</t>
+          <t>https://job-boards.greenhouse.io/warburgpincusllc</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://financewalk.com/top-private-equity-firms/</t>
+          <t>https://job-boards.greenhouse.io/tpgcareers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://mergersandinquisitions.com/private-equity/careers/</t>
+          <t>https://www.truenorth.co.in/careers/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/generalatlantic/jobs/5430747004</t>
+          <t>https://job-boards.greenhouse.io/generalatlantic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://blackstone.wd1.myworkdayjobs.com/Blackstone_Careers</t>
+          <t>https://blackstone.wd1.myworkdayjobs.com/en-US/Blackstone_Careers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2417,11 +2417,7 @@
           <t>Private Equity</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>https://jobs.fulcrumep.com/jobs</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/fulcrum-venture-india/jobs/</t>
@@ -2539,7 +2535,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/generalatlantic/jobs/5553872004</t>
+          <t>https://jobs.lever.co/act</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2869,7 +2865,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://baincapital.wd1.myworkdayjobs.com/external_public</t>
+          <t>https://baincapital.wd1.myworkdayjobs.com/External_Public</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4877,11 +4873,7 @@
           <t>Private Equity</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>https://inforcapital.com/jobs/private-equity/london/</t>
-        </is>
-      </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/greater-pacific-capital/jobs/</t>
@@ -4957,7 +4949,6 @@
           <t>Nippon</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
           <t>Private Equity</t>
